--- a/manual_scripts/gas_updated_corrected_states.xlsx
+++ b/manual_scripts/gas_updated_corrected_states.xlsx
@@ -15673,7 +15673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="true">
+  <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K539"/>
@@ -15718,7 +15718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -15747,7 +15747,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -15782,7 +15782,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
@@ -15817,7 +15817,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -15849,7 +15849,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -15881,7 +15881,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -15916,7 +15916,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -15951,7 +15951,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -15986,7 +15986,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -16012,7 +16012,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
@@ -16035,7 +16035,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
@@ -16067,7 +16067,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
@@ -16099,7 +16099,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
@@ -16131,7 +16131,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -16163,7 +16163,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
@@ -16195,7 +16195,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>35</v>
       </c>
@@ -16227,7 +16227,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -16262,7 +16262,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>38</v>
       </c>
@@ -16288,7 +16288,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>38</v>
       </c>
@@ -16317,7 +16317,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -16349,7 +16349,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
         <v>18</v>
       </c>
@@ -16381,7 +16381,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
         <v>43</v>
       </c>
@@ -16413,7 +16413,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
         <v>45</v>
       </c>
@@ -16445,7 +16445,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -16477,7 +16477,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
         <v>38</v>
       </c>
@@ -16509,7 +16509,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
         <v>32</v>
       </c>
@@ -16541,7 +16541,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>18</v>
       </c>
@@ -16573,7 +16573,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
         <v>48</v>
       </c>
@@ -16605,7 +16605,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
         <v>49</v>
       </c>
@@ -16637,7 +16637,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
         <v>38</v>
       </c>
@@ -16669,7 +16669,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
         <v>50</v>
       </c>
@@ -16701,7 +16701,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
         <v>51</v>
       </c>
@@ -16733,7 +16733,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
         <v>52</v>
       </c>
@@ -16765,7 +16765,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
         <v>45</v>
       </c>
@@ -16797,7 +16797,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
         <v>11</v>
       </c>
@@ -16829,7 +16829,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
         <v>35</v>
       </c>
@@ -16861,7 +16861,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
         <v>32</v>
       </c>
@@ -16893,7 +16893,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
         <v>32</v>
       </c>
@@ -16925,7 +16925,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
         <v>32</v>
       </c>
@@ -16957,7 +16957,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
         <v>54</v>
       </c>
@@ -16989,7 +16989,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
         <v>55</v>
       </c>
@@ -17021,7 +17021,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
         <v>56</v>
       </c>
@@ -17053,7 +17053,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
         <v>56</v>
       </c>
@@ -17085,7 +17085,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
         <v>18</v>
       </c>
@@ -17117,7 +17117,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
         <v>11</v>
       </c>
@@ -17149,7 +17149,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
         <v>32</v>
       </c>
@@ -17181,7 +17181,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
         <v>38</v>
       </c>
@@ -17213,7 +17213,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
         <v>32</v>
       </c>
@@ -17245,7 +17245,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
         <v>18</v>
       </c>
@@ -17277,7 +17277,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
         <v>60</v>
       </c>
@@ -17309,7 +17309,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
         <v>28</v>
       </c>
@@ -17341,7 +17341,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
         <v>18</v>
       </c>
@@ -17376,7 +17376,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
         <v>35</v>
       </c>
@@ -17411,7 +17411,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
         <v>63</v>
       </c>
@@ -17446,7 +17446,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
         <v>32</v>
       </c>
@@ -17481,7 +17481,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>56</v>
       </c>
@@ -17516,7 +17516,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
         <v>60</v>
       </c>
@@ -17551,7 +17551,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
         <v>43</v>
       </c>
@@ -17586,7 +17586,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
         <v>18</v>
       </c>
@@ -17618,7 +17618,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
         <v>18</v>
       </c>
@@ -17650,7 +17650,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
         <v>11</v>
       </c>
@@ -17682,7 +17682,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
         <v>32</v>
       </c>
@@ -17714,7 +17714,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
         <v>43</v>
       </c>
@@ -17746,7 +17746,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
         <v>11</v>
       </c>
@@ -17778,7 +17778,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
         <v>28</v>
       </c>
@@ -17810,7 +17810,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
         <v>38</v>
       </c>
@@ -17842,7 +17842,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
         <v>11</v>
       </c>
@@ -17874,7 +17874,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
         <v>49</v>
       </c>
@@ -17906,7 +17906,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
         <v>32</v>
       </c>
@@ -17938,7 +17938,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
         <v>11</v>
       </c>
@@ -17973,7 +17973,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
         <v>11</v>
       </c>
@@ -18005,7 +18005,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
         <v>43</v>
       </c>
@@ -18031,7 +18031,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
         <v>43</v>
       </c>
@@ -18057,7 +18057,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
         <v>11</v>
       </c>
@@ -18083,7 +18083,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
         <v>11</v>
       </c>
@@ -18109,7 +18109,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
         <v>51</v>
       </c>
@@ -18141,7 +18141,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
         <v>18</v>
       </c>
@@ -18173,7 +18173,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
         <v>75</v>
       </c>
@@ -18205,7 +18205,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
         <v>38</v>
       </c>
@@ -18237,7 +18237,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
         <v>78</v>
       </c>
@@ -18269,7 +18269,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
         <v>79</v>
       </c>
@@ -18301,7 +18301,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
         <v>43</v>
       </c>
@@ -18333,7 +18333,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
         <v>80</v>
       </c>
@@ -18365,7 +18365,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
         <v>56</v>
       </c>
@@ -18397,7 +18397,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
         <v>18</v>
       </c>
@@ -18429,7 +18429,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
         <v>38</v>
       </c>
@@ -18461,7 +18461,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
         <v>56</v>
       </c>
@@ -18493,7 +18493,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
@@ -18525,7 +18525,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
         <v>83</v>
       </c>
@@ -18551,7 +18551,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
         <v>11</v>
       </c>
@@ -18577,7 +18577,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
         <v>18</v>
       </c>
@@ -18609,7 +18609,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
         <v>28</v>
       </c>
@@ -18641,7 +18641,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
         <v>18</v>
       </c>
@@ -18676,7 +18676,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
         <v>56</v>
       </c>
@@ -18702,7 +18702,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
         <v>56</v>
       </c>
@@ -18728,7 +18728,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
         <v>18</v>
       </c>
@@ -18754,7 +18754,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
         <v>11</v>
       </c>
@@ -18780,7 +18780,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
         <v>18</v>
       </c>
@@ -18812,7 +18812,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
         <v>92</v>
       </c>
@@ -18844,7 +18844,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
         <v>56</v>
       </c>
@@ -18876,7 +18876,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
         <v>43</v>
       </c>
@@ -18908,7 +18908,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
         <v>11</v>
       </c>
@@ -18934,7 +18934,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
         <v>18</v>
       </c>
@@ -18966,7 +18966,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
         <v>38</v>
       </c>
@@ -18998,7 +18998,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
         <v>51</v>
       </c>
@@ -19030,7 +19030,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
         <v>56</v>
       </c>
@@ -19062,7 +19062,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
         <v>18</v>
       </c>
@@ -19094,7 +19094,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
         <v>18</v>
       </c>
@@ -19126,7 +19126,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
         <v>28</v>
       </c>
@@ -19158,7 +19158,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
         <v>38</v>
       </c>
@@ -19190,7 +19190,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
         <v>56</v>
       </c>
@@ -19222,7 +19222,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
         <v>56</v>
       </c>
@@ -19254,7 +19254,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
         <v>52</v>
       </c>
@@ -19280,7 +19280,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
         <v>18</v>
       </c>
@@ -19306,7 +19306,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
         <v>18</v>
       </c>
@@ -19332,7 +19332,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
         <v>43</v>
       </c>
@@ -19358,7 +19358,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
         <v>52</v>
       </c>
@@ -19384,7 +19384,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
         <v>52</v>
       </c>
@@ -19410,7 +19410,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
         <v>18</v>
       </c>
@@ -19436,7 +19436,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
         <v>18</v>
       </c>
@@ -19462,7 +19462,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
         <v>50</v>
       </c>
@@ -19488,7 +19488,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
         <v>50</v>
       </c>
@@ -19514,7 +19514,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
         <v>43</v>
       </c>
@@ -19540,7 +19540,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
         <v>43</v>
       </c>
@@ -19566,7 +19566,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
         <v>11</v>
       </c>
@@ -19592,7 +19592,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
         <v>11</v>
       </c>
@@ -19618,7 +19618,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
         <v>18</v>
       </c>
@@ -19644,7 +19644,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
         <v>101</v>
       </c>
@@ -19670,7 +19670,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
         <v>11</v>
       </c>
@@ -19696,7 +19696,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
         <v>56</v>
       </c>
@@ -19722,7 +19722,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
         <v>32</v>
       </c>
@@ -19754,7 +19754,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
         <v>56</v>
       </c>
@@ -19786,7 +19786,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
         <v>38</v>
       </c>
@@ -19812,7 +19812,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
         <v>101</v>
       </c>
@@ -19838,7 +19838,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
         <v>11</v>
       </c>
@@ -19864,7 +19864,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
         <v>43</v>
       </c>
@@ -19890,7 +19890,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
         <v>11</v>
       </c>
@@ -19916,7 +19916,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
         <v>11</v>
       </c>
@@ -19951,7 +19951,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
         <v>11</v>
       </c>
@@ -19986,7 +19986,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
         <v>56</v>
       </c>
@@ -20021,7 +20021,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
         <v>43</v>
       </c>
@@ -20056,7 +20056,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
         <v>11</v>
       </c>
@@ -20082,7 +20082,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
         <v>38</v>
       </c>
@@ -20108,7 +20108,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
         <v>111</v>
       </c>
@@ -20134,7 +20134,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
         <v>38</v>
       </c>
@@ -20160,7 +20160,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
         <v>56</v>
       </c>
@@ -20186,7 +20186,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
         <v>18</v>
       </c>
@@ -20212,7 +20212,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
         <v>56</v>
       </c>
@@ -20238,7 +20238,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
         <v>56</v>
       </c>
@@ -20273,7 +20273,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
         <v>18</v>
       </c>
@@ -20305,7 +20305,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
         <v>116</v>
       </c>
@@ -20337,7 +20337,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
         <v>116</v>
       </c>
@@ -20369,7 +20369,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
         <v>38</v>
       </c>
@@ -20401,7 +20401,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
         <v>32</v>
       </c>
@@ -20433,7 +20433,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
         <v>50</v>
       </c>
@@ -20465,7 +20465,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
         <v>56</v>
       </c>
@@ -20497,7 +20497,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
         <v>56</v>
       </c>
@@ -20529,7 +20529,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
         <v>56</v>
       </c>
@@ -20564,7 +20564,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
         <v>56</v>
       </c>
@@ -20596,7 +20596,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
         <v>28</v>
       </c>
@@ -20628,7 +20628,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
         <v>56</v>
       </c>
@@ -20663,7 +20663,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2" t="s">
         <v>49</v>
       </c>
@@ -20692,7 +20692,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
         <v>56</v>
       </c>
@@ -20727,7 +20727,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
         <v>18</v>
       </c>
@@ -20762,7 +20762,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="s">
         <v>38</v>
       </c>
@@ -20797,7 +20797,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="s">
         <v>56</v>
       </c>
@@ -20832,7 +20832,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="s">
         <v>52</v>
       </c>
@@ -20867,7 +20867,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
         <v>56</v>
       </c>
@@ -20902,7 +20902,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
         <v>28</v>
       </c>
@@ -20937,7 +20937,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="s">
         <v>56</v>
       </c>
@@ -20972,7 +20972,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="s">
         <v>127</v>
       </c>
@@ -21004,7 +21004,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
         <v>127</v>
       </c>
@@ -21030,7 +21030,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="s">
         <v>18</v>
       </c>
@@ -21062,7 +21062,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="s">
         <v>18</v>
       </c>
@@ -21094,7 +21094,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
         <v>11</v>
       </c>
@@ -21126,7 +21126,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="s">
         <v>11</v>
       </c>
@@ -21152,7 +21152,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="s">
         <v>49</v>
       </c>
@@ -21184,7 +21184,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2" t="s">
         <v>38</v>
       </c>
@@ -21216,7 +21216,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
         <v>32</v>
       </c>
@@ -21248,7 +21248,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
         <v>32</v>
       </c>
@@ -21280,7 +21280,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="2" t="s">
         <v>56</v>
       </c>
@@ -21312,7 +21312,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="s">
         <v>130</v>
       </c>
@@ -21341,7 +21341,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2" t="s">
         <v>11</v>
       </c>
@@ -21376,7 +21376,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="2" t="s">
         <v>56</v>
       </c>
@@ -21402,7 +21402,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="2" t="s">
         <v>18</v>
       </c>
@@ -21437,7 +21437,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2" t="s">
         <v>32</v>
       </c>
@@ -21472,7 +21472,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="2" t="s">
         <v>127</v>
       </c>
@@ -21504,7 +21504,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2" t="s">
         <v>127</v>
       </c>
@@ -21536,7 +21536,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2" t="s">
         <v>35</v>
       </c>
@@ -21568,7 +21568,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="s">
         <v>134</v>
       </c>
@@ -21600,7 +21600,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="2" t="s">
         <v>38</v>
       </c>
@@ -21632,7 +21632,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="s">
         <v>38</v>
       </c>
@@ -21658,7 +21658,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2" t="s">
         <v>32</v>
       </c>
@@ -21690,7 +21690,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2" t="s">
         <v>56</v>
       </c>
@@ -21722,7 +21722,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2" t="s">
         <v>56</v>
       </c>
@@ -21748,7 +21748,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="s">
         <v>43</v>
       </c>
@@ -21780,7 +21780,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
         <v>18</v>
       </c>
@@ -21815,7 +21815,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="s">
         <v>32</v>
       </c>
@@ -21850,7 +21850,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="s">
         <v>56</v>
       </c>
@@ -21885,7 +21885,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="s">
         <v>18</v>
       </c>
@@ -21920,7 +21920,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="s">
         <v>11</v>
       </c>
@@ -21955,7 +21955,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="s">
         <v>116</v>
       </c>
@@ -21990,7 +21990,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
         <v>32</v>
       </c>
@@ -22025,7 +22025,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2" t="s">
         <v>56</v>
       </c>
@@ -22060,7 +22060,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2" t="s">
         <v>18</v>
       </c>
@@ -22086,7 +22086,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="s">
         <v>11</v>
       </c>
@@ -22112,7 +22112,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
         <v>38</v>
       </c>
@@ -22144,7 +22144,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2" t="s">
         <v>78</v>
       </c>
@@ -22176,7 +22176,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2" t="s">
         <v>79</v>
       </c>
@@ -22208,7 +22208,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2" t="s">
         <v>56</v>
       </c>
@@ -22240,7 +22240,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2" t="s">
         <v>56</v>
       </c>
@@ -22266,7 +22266,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2" t="s">
         <v>138</v>
       </c>
@@ -22298,7 +22298,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2" t="s">
         <v>18</v>
       </c>
@@ -22333,7 +22333,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2" t="s">
         <v>35</v>
       </c>
@@ -22368,7 +22368,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2" t="s">
         <v>32</v>
       </c>
@@ -22403,7 +22403,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2" t="s">
         <v>56</v>
       </c>
@@ -22438,7 +22438,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2" t="s">
         <v>60</v>
       </c>
@@ -22473,7 +22473,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2" t="s">
         <v>18</v>
       </c>
@@ -22508,7 +22508,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
         <v>32</v>
       </c>
@@ -22543,7 +22543,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2" t="s">
         <v>22</v>
       </c>
@@ -22578,7 +22578,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2" t="s">
         <v>63</v>
       </c>
@@ -22613,7 +22613,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2" t="s">
         <v>38</v>
       </c>
@@ -22648,7 +22648,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2" t="s">
         <v>18</v>
       </c>
@@ -22680,7 +22680,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2" t="s">
         <v>32</v>
       </c>
@@ -22712,7 +22712,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2" t="s">
         <v>55</v>
       </c>
@@ -22744,7 +22744,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2" t="s">
         <v>50</v>
       </c>
@@ -22776,7 +22776,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2" t="s">
         <v>51</v>
       </c>
@@ -22808,7 +22808,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2" t="s">
         <v>56</v>
       </c>
@@ -22840,7 +22840,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2" t="s">
         <v>38</v>
       </c>
@@ -22866,7 +22866,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2" t="s">
         <v>101</v>
       </c>
@@ -22892,7 +22892,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="2" t="s">
         <v>56</v>
       </c>
@@ -22918,7 +22918,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2" t="s">
         <v>38</v>
       </c>
@@ -22944,7 +22944,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="2" t="s">
         <v>38</v>
       </c>
@@ -22967,7 +22967,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="2" t="s">
         <v>147</v>
       </c>
@@ -23002,7 +23002,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="2" t="s">
         <v>11</v>
       </c>
@@ -23037,7 +23037,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="2" t="s">
         <v>11</v>
       </c>
@@ -23072,7 +23072,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2" t="s">
         <v>35</v>
       </c>
@@ -23107,7 +23107,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="2" t="s">
         <v>48</v>
       </c>
@@ -23142,7 +23142,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="2" t="s">
         <v>149</v>
       </c>
@@ -23177,7 +23177,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="2" t="s">
         <v>51</v>
       </c>
@@ -23212,7 +23212,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2" t="s">
         <v>51</v>
       </c>
@@ -23247,7 +23247,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2" t="s">
         <v>150</v>
       </c>
@@ -23282,7 +23282,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2" t="s">
         <v>45</v>
       </c>
@@ -23317,7 +23317,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2" t="s">
         <v>45</v>
       </c>
@@ -23352,7 +23352,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="2" t="s">
         <v>18</v>
       </c>
@@ -23387,7 +23387,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="2" t="s">
         <v>11</v>
       </c>
@@ -23422,7 +23422,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2" t="s">
         <v>50</v>
       </c>
@@ -23457,7 +23457,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="2" t="s">
         <v>56</v>
       </c>
@@ -23492,7 +23492,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="2" t="s">
         <v>56</v>
       </c>
@@ -23527,7 +23527,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="2" t="s">
         <v>43</v>
       </c>
@@ -23562,7 +23562,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="2" t="s">
         <v>45</v>
       </c>
@@ -23597,7 +23597,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2" t="s">
         <v>11</v>
       </c>
@@ -23632,7 +23632,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="2" t="s">
         <v>35</v>
       </c>
@@ -23667,7 +23667,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="2" t="s">
         <v>101</v>
       </c>
@@ -23702,7 +23702,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="2" t="s">
         <v>38</v>
       </c>
@@ -23737,7 +23737,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="2" t="s">
         <v>38</v>
       </c>
@@ -23772,7 +23772,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="2" t="s">
         <v>38</v>
       </c>
@@ -23807,7 +23807,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="2" t="s">
         <v>38</v>
       </c>
@@ -23842,7 +23842,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="2" t="s">
         <v>32</v>
       </c>
@@ -23877,7 +23877,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="2" t="s">
         <v>32</v>
       </c>
@@ -23912,7 +23912,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="2" t="s">
         <v>153</v>
       </c>
@@ -23947,7 +23947,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="2" t="s">
         <v>45</v>
       </c>
@@ -23982,7 +23982,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="2" t="s">
         <v>56</v>
       </c>
@@ -24017,7 +24017,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="2" t="s">
         <v>18</v>
       </c>
@@ -24052,7 +24052,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="2" t="s">
         <v>56</v>
       </c>
@@ -24087,7 +24087,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2" t="s">
         <v>28</v>
       </c>
@@ -24122,7 +24122,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="2" t="s">
         <v>18</v>
       </c>
@@ -24157,7 +24157,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="2" t="s">
         <v>22</v>
       </c>
@@ -24192,7 +24192,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="2" t="s">
         <v>38</v>
       </c>
@@ -24227,7 +24227,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="2" t="s">
         <v>43</v>
       </c>
@@ -24262,7 +24262,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="2" t="s">
         <v>18</v>
       </c>
@@ -24297,7 +24297,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="273" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="2" t="s">
         <v>11</v>
       </c>
@@ -24332,7 +24332,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="2" t="s">
         <v>11</v>
       </c>
@@ -24367,7 +24367,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="2" t="s">
         <v>56</v>
       </c>
@@ -24402,7 +24402,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="2" t="s">
         <v>56</v>
       </c>
@@ -24437,7 +24437,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="2" t="s">
         <v>38</v>
       </c>
@@ -24469,7 +24469,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="2" t="s">
         <v>56</v>
       </c>
@@ -24501,7 +24501,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="2" t="s">
         <v>18</v>
       </c>
@@ -24536,7 +24536,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="2" t="s">
         <v>56</v>
       </c>
@@ -24571,7 +24571,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="2" t="s">
         <v>56</v>
       </c>
@@ -24664,7 +24664,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="2" t="s">
         <v>18</v>
       </c>
@@ -24690,7 +24690,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="2" t="s">
         <v>11</v>
       </c>
@@ -24716,7 +24716,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="2" t="s">
         <v>56</v>
       </c>
@@ -24742,7 +24742,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="2" t="s">
         <v>51</v>
       </c>
@@ -24777,7 +24777,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="288" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="2" t="s">
         <v>18</v>
       </c>
@@ -24803,7 +24803,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="2" t="s">
         <v>38</v>
       </c>
@@ -24829,7 +24829,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="290" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="2" t="s">
         <v>50</v>
       </c>
@@ -24861,7 +24861,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="291" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="2" t="s">
         <v>18</v>
       </c>
@@ -24887,7 +24887,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2" t="s">
         <v>11</v>
       </c>
@@ -24913,7 +24913,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="293" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="2" t="s">
         <v>38</v>
       </c>
@@ -24939,7 +24939,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="294" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="2" t="s">
         <v>56</v>
       </c>
@@ -24965,7 +24965,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="295" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="2" t="s">
         <v>52</v>
       </c>
@@ -24991,7 +24991,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="2" t="s">
         <v>43</v>
       </c>
@@ -25017,7 +25017,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="2" t="s">
         <v>56</v>
       </c>
@@ -25043,7 +25043,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="298" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="2" t="s">
         <v>43</v>
       </c>
@@ -25069,7 +25069,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="2" t="s">
         <v>11</v>
       </c>
@@ -25098,7 +25098,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="2" t="s">
         <v>18</v>
       </c>
@@ -25124,7 +25124,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="301" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="2" t="s">
         <v>38</v>
       </c>
@@ -25159,7 +25159,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="2" t="s">
         <v>56</v>
       </c>
@@ -25194,7 +25194,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="2" t="s">
         <v>38</v>
       </c>
@@ -25229,7 +25229,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="304" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="2" t="s">
         <v>56</v>
       </c>
@@ -25264,7 +25264,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="2" t="s">
         <v>56</v>
       </c>
@@ -25290,7 +25290,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="306" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="2" t="s">
         <v>56</v>
       </c>
@@ -25325,7 +25325,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="307" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="307" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="2" t="s">
         <v>43</v>
       </c>
@@ -25360,7 +25360,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="308" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="2" t="s">
         <v>56</v>
       </c>
@@ -25395,7 +25395,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="309" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="2" t="s">
         <v>43</v>
       </c>
@@ -25430,7 +25430,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="310" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="2" t="s">
         <v>56</v>
       </c>
@@ -25465,7 +25465,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="311" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="2" t="s">
         <v>56</v>
       </c>
@@ -25491,7 +25491,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="312" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="2" t="s">
         <v>178</v>
       </c>
@@ -25526,7 +25526,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="2" t="s">
         <v>18</v>
       </c>
@@ -25561,7 +25561,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="2" t="s">
         <v>18</v>
       </c>
@@ -25596,7 +25596,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="2" t="s">
         <v>38</v>
       </c>
@@ -25631,7 +25631,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="316" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="2" t="s">
         <v>32</v>
       </c>
@@ -25666,7 +25666,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="2" t="s">
         <v>43</v>
       </c>
@@ -25701,7 +25701,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="2" t="s">
         <v>56</v>
       </c>
@@ -25736,7 +25736,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="319" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="2" t="s">
         <v>18</v>
       </c>
@@ -25762,7 +25762,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="320" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="2" t="s">
         <v>38</v>
       </c>
@@ -25788,7 +25788,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="2" t="s">
         <v>32</v>
       </c>
@@ -25814,7 +25814,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="322" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="2" t="s">
         <v>43</v>
       </c>
@@ -25840,7 +25840,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="323" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="2" t="s">
         <v>18</v>
       </c>
@@ -25866,7 +25866,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="324" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="2" t="s">
         <v>38</v>
       </c>
@@ -25892,7 +25892,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="325" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="2" t="s">
         <v>38</v>
       </c>
@@ -25924,7 +25924,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="326" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="2" t="s">
         <v>38</v>
       </c>
@@ -25950,7 +25950,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="327" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="327" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="2" t="s">
         <v>38</v>
       </c>
@@ -25976,7 +25976,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="328" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="328" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="2" t="s">
         <v>52</v>
       </c>
@@ -26002,7 +26002,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="329" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="329" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="2" t="s">
         <v>43</v>
       </c>
@@ -26028,7 +26028,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="330" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="330" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="2" t="s">
         <v>11</v>
       </c>
@@ -26054,7 +26054,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="331" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="331" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="2" t="s">
         <v>51</v>
       </c>
@@ -26080,7 +26080,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="332" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="332" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="2" t="s">
         <v>56</v>
       </c>
@@ -26106,7 +26106,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="333" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="333" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="2" t="s">
         <v>56</v>
       </c>
@@ -26132,7 +26132,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="334" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="2" t="s">
         <v>38</v>
       </c>
@@ -26158,7 +26158,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="335" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="2" t="s">
         <v>38</v>
       </c>
@@ -26184,7 +26184,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="336" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="2" t="s">
         <v>56</v>
       </c>
@@ -26210,7 +26210,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="337" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="2" t="s">
         <v>18</v>
       </c>
@@ -26245,7 +26245,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="338" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="2" t="s">
         <v>35</v>
       </c>
@@ -26280,7 +26280,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="339" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="2" t="s">
         <v>38</v>
       </c>
@@ -26315,7 +26315,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="340" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="2" t="s">
         <v>32</v>
       </c>
@@ -26350,7 +26350,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="341" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="341" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="2" t="s">
         <v>51</v>
       </c>
@@ -26385,7 +26385,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="342" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="342" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="2" t="s">
         <v>43</v>
       </c>
@@ -26420,7 +26420,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="343" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="343" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="2" t="s">
         <v>50</v>
       </c>
@@ -26446,7 +26446,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="344" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="2" t="s">
         <v>50</v>
       </c>
@@ -26472,7 +26472,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="345" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="2" t="s">
         <v>51</v>
       </c>
@@ -26498,7 +26498,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="346" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="346" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="2" t="s">
         <v>51</v>
       </c>
@@ -26524,7 +26524,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="347" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="2" t="s">
         <v>83</v>
       </c>
@@ -26550,7 +26550,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="348" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="2" t="s">
         <v>127</v>
       </c>
@@ -26585,7 +26585,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="349" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="2" t="s">
         <v>18</v>
       </c>
@@ -26620,7 +26620,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="350" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="2" t="s">
         <v>18</v>
       </c>
@@ -26646,7 +26646,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="351" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="2" t="s">
         <v>11</v>
       </c>
@@ -26681,7 +26681,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="352" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="2" t="s">
         <v>35</v>
       </c>
@@ -26716,7 +26716,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="353" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="2" t="s">
         <v>38</v>
       </c>
@@ -26751,7 +26751,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="354" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="2" t="s">
         <v>38</v>
       </c>
@@ -26777,7 +26777,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="355" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="2" t="s">
         <v>32</v>
       </c>
@@ -26812,7 +26812,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="356" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="2" t="s">
         <v>193</v>
       </c>
@@ -26847,7 +26847,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="357" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="2" t="s">
         <v>43</v>
       </c>
@@ -26882,7 +26882,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="358" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2" t="s">
         <v>11</v>
       </c>
@@ -26914,7 +26914,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="359" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="359" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="2" t="s">
         <v>32</v>
       </c>
@@ -26946,7 +26946,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="360" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="2" t="s">
         <v>56</v>
       </c>
@@ -26978,7 +26978,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="361" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="361" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="2" t="s">
         <v>51</v>
       </c>
@@ -27004,7 +27004,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="362" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="362" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="2" t="s">
         <v>196</v>
       </c>
@@ -27030,7 +27030,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="363" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="2" t="s">
         <v>130</v>
       </c>
@@ -27056,7 +27056,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="364" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="2" t="s">
         <v>198</v>
       </c>
@@ -27082,7 +27082,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="365" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="365" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="2" t="s">
         <v>83</v>
       </c>
@@ -27108,7 +27108,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="366" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="2" t="s">
         <v>49</v>
       </c>
@@ -27140,7 +27140,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="367" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="367" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="2" t="s">
         <v>18</v>
       </c>
@@ -27172,7 +27172,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="368" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="2" t="s">
         <v>28</v>
       </c>
@@ -27204,7 +27204,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="369" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="2" t="s">
         <v>56</v>
       </c>
@@ -27236,7 +27236,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="370" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="2" t="s">
         <v>43</v>
       </c>
@@ -27268,7 +27268,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="371" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="371" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="2" t="s">
         <v>18</v>
       </c>
@@ -27294,7 +27294,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="372" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="2" t="s">
         <v>18</v>
       </c>
@@ -27326,7 +27326,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="373" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="2" t="s">
         <v>11</v>
       </c>
@@ -27352,7 +27352,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="374" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="2" t="s">
         <v>11</v>
       </c>
@@ -27378,7 +27378,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="375" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="375" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="2" t="s">
         <v>38</v>
       </c>
@@ -27404,7 +27404,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="376" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="2" t="s">
         <v>56</v>
       </c>
@@ -27430,7 +27430,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="377" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="377" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="2" t="s">
         <v>18</v>
       </c>
@@ -27456,7 +27456,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="378" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="378" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="2" t="s">
         <v>52</v>
       </c>
@@ -27482,7 +27482,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="379" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="379" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="2" t="s">
         <v>18</v>
       </c>
@@ -27508,7 +27508,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="380" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="380" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="2" t="s">
         <v>206</v>
       </c>
@@ -27534,7 +27534,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="381" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="2" t="s">
         <v>49</v>
       </c>
@@ -27560,7 +27560,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="382" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="2" t="s">
         <v>43</v>
       </c>
@@ -27586,7 +27586,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="383" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="2" t="s">
         <v>43</v>
       </c>
@@ -27612,7 +27612,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="384" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="384" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="2" t="s">
         <v>18</v>
       </c>
@@ -27647,7 +27647,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="385" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="2" t="s">
         <v>56</v>
       </c>
@@ -27682,7 +27682,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="386" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="386" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="2" t="s">
         <v>43</v>
       </c>
@@ -27717,7 +27717,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="387" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="387" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="2" t="s">
         <v>32</v>
       </c>
@@ -27752,7 +27752,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="388" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="2" t="s">
         <v>18</v>
       </c>
@@ -27778,7 +27778,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="389" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="2" t="s">
         <v>11</v>
       </c>
@@ -27804,7 +27804,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="390" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="2" t="s">
         <v>32</v>
       </c>
@@ -27830,7 +27830,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="391" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="2" t="s">
         <v>50</v>
       </c>
@@ -27856,7 +27856,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="392" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="2" t="s">
         <v>56</v>
       </c>
@@ -27882,7 +27882,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="393" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="2" t="s">
         <v>43</v>
       </c>
@@ -27908,7 +27908,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="394" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="394" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="2" t="s">
         <v>18</v>
       </c>
@@ -27940,7 +27940,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="395" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="2" t="s">
         <v>18</v>
       </c>
@@ -27972,7 +27972,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="396" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="396" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="2" t="s">
         <v>11</v>
       </c>
@@ -27998,7 +27998,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="397" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="397" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="2" t="s">
         <v>49</v>
       </c>
@@ -28030,7 +28030,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="398" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="398" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="2" t="s">
         <v>211</v>
       </c>
@@ -28062,7 +28062,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="399" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="399" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="2" t="s">
         <v>38</v>
       </c>
@@ -28094,7 +28094,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="400" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="2" t="s">
         <v>38</v>
       </c>
@@ -28126,7 +28126,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="401" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="2" t="s">
         <v>38</v>
       </c>
@@ -28152,7 +28152,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="402" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="402" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2" t="s">
         <v>32</v>
       </c>
@@ -28184,7 +28184,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="403" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="403" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="2" t="s">
         <v>56</v>
       </c>
@@ -28216,7 +28216,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="404" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="404" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="2" t="s">
         <v>56</v>
       </c>
@@ -28248,7 +28248,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="405" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="405" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="2" t="s">
         <v>43</v>
       </c>
@@ -28280,7 +28280,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="406" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="406" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="2" t="s">
         <v>11</v>
       </c>
@@ -28306,7 +28306,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="407" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="2" t="s">
         <v>11</v>
       </c>
@@ -28338,7 +28338,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="408" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="408" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="2" t="s">
         <v>28</v>
       </c>
@@ -28370,7 +28370,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="409" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="2" t="s">
         <v>56</v>
       </c>
@@ -28402,7 +28402,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="410" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="410" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="2" t="s">
         <v>18</v>
       </c>
@@ -28434,7 +28434,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="411" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="2" t="s">
         <v>38</v>
       </c>
@@ -28466,7 +28466,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="412" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="412" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="2" t="s">
         <v>38</v>
       </c>
@@ -28498,7 +28498,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="413" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="413" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="2" t="s">
         <v>38</v>
       </c>
@@ -28530,7 +28530,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="414" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="2" t="s">
         <v>56</v>
       </c>
@@ -28562,7 +28562,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="415" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="2" t="s">
         <v>45</v>
       </c>
@@ -28594,7 +28594,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="416" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="2" t="s">
         <v>18</v>
       </c>
@@ -28626,7 +28626,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="417" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="2" t="s">
         <v>56</v>
       </c>
@@ -28658,7 +28658,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="418" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="418" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="2" t="s">
         <v>56</v>
       </c>
@@ -28690,7 +28690,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="419" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="419" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="2" t="s">
         <v>56</v>
       </c>
@@ -28722,7 +28722,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="420" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="420" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="2" t="s">
         <v>22</v>
       </c>
@@ -28757,7 +28757,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="421" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="421" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="2" t="s">
         <v>56</v>
       </c>
@@ -28792,7 +28792,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="422" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="422" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="2" t="s">
         <v>56</v>
       </c>
@@ -28827,7 +28827,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="423" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="423" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="2" t="s">
         <v>18</v>
       </c>
@@ -28859,7 +28859,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="424" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="424" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="2" t="s">
         <v>56</v>
       </c>
@@ -28891,7 +28891,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="425" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2" t="s">
         <v>18</v>
       </c>
@@ -28926,7 +28926,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="426" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2" t="s">
         <v>56</v>
       </c>
@@ -28961,7 +28961,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="427" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="2" t="s">
         <v>18</v>
       </c>
@@ -28993,7 +28993,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="428" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="428" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2" t="s">
         <v>11</v>
       </c>
@@ -29025,7 +29025,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="429" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="2" t="s">
         <v>56</v>
       </c>
@@ -29057,7 +29057,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="430" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="2" t="s">
         <v>56</v>
       </c>
@@ -29092,7 +29092,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="431" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="431" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="2" t="s">
         <v>18</v>
       </c>
@@ -29124,7 +29124,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="432" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2" t="s">
         <v>11</v>
       </c>
@@ -29156,7 +29156,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="433" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="2" t="s">
         <v>56</v>
       </c>
@@ -29188,7 +29188,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="434" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="434" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="2" t="s">
         <v>18</v>
       </c>
@@ -29220,7 +29220,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="435" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="2" t="s">
         <v>18</v>
       </c>
@@ -29246,7 +29246,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="436" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="2" t="s">
         <v>18</v>
       </c>
@@ -29278,7 +29278,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="437" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2" t="s">
         <v>38</v>
       </c>
@@ -29310,7 +29310,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="438" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="2" t="s">
         <v>52</v>
       </c>
@@ -29336,7 +29336,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="439" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="2" t="s">
         <v>18</v>
       </c>
@@ -29362,7 +29362,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="440" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="440" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="2" t="s">
         <v>18</v>
       </c>
@@ -29391,7 +29391,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="441" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="441" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="2" t="s">
         <v>43</v>
       </c>
@@ -29417,7 +29417,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="442" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="2" t="s">
         <v>18</v>
       </c>
@@ -29452,7 +29452,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="443" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="443" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2" t="s">
         <v>18</v>
       </c>
@@ -29487,7 +29487,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="444" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="444" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="2" t="s">
         <v>18</v>
       </c>
@@ -29522,7 +29522,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="445" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="445" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="2" t="s">
         <v>56</v>
       </c>
@@ -29554,7 +29554,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="446" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="446" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2" t="s">
         <v>18</v>
       </c>
@@ -29589,7 +29589,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="447" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="447" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="2" t="s">
         <v>28</v>
       </c>
@@ -29624,7 +29624,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="448" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="2" t="s">
         <v>18</v>
       </c>
@@ -29656,7 +29656,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="449" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="2" t="s">
         <v>28</v>
       </c>
@@ -29688,7 +29688,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="450" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="450" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="2" t="s">
         <v>56</v>
       </c>
@@ -29720,7 +29720,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="451" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="2" t="s">
         <v>43</v>
       </c>
@@ -29752,7 +29752,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="452" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="452" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="2" t="s">
         <v>18</v>
       </c>
@@ -29784,7 +29784,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="453" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="453" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="2" t="s">
         <v>28</v>
       </c>
@@ -29816,7 +29816,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="454" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="454" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="2" t="s">
         <v>56</v>
       </c>
@@ -29848,7 +29848,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="455" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="455" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="2" t="s">
         <v>56</v>
       </c>
@@ -29874,7 +29874,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="456" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="456" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2" t="s">
         <v>18</v>
       </c>
@@ -29909,7 +29909,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="457" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2" t="s">
         <v>28</v>
       </c>
@@ -29944,7 +29944,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="458" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="458" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2" t="s">
         <v>56</v>
       </c>
@@ -29979,7 +29979,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="459" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="459" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="2" t="s">
         <v>18</v>
       </c>
@@ -30011,7 +30011,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="460" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="460" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="2" t="s">
         <v>56</v>
       </c>
@@ -30043,7 +30043,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="461" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="461" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="2" t="s">
         <v>32</v>
       </c>
@@ -30075,7 +30075,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="462" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="462" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="2" t="s">
         <v>18</v>
       </c>
@@ -30107,7 +30107,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="463" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="463" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="2" t="s">
         <v>80</v>
       </c>
@@ -30139,7 +30139,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="464" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="2" t="s">
         <v>32</v>
       </c>
@@ -30171,7 +30171,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="465" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="465" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="2" t="s">
         <v>56</v>
       </c>
@@ -30203,7 +30203,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="466" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="466" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="2" t="s">
         <v>38</v>
       </c>
@@ -30229,7 +30229,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="467" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="467" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="2" t="s">
         <v>56</v>
       </c>
@@ -30255,7 +30255,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="468" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="468" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2" t="s">
         <v>11</v>
       </c>
@@ -30281,7 +30281,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="469" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="469" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="2" t="s">
         <v>18</v>
       </c>
@@ -30307,7 +30307,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="470" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="2" t="s">
         <v>38</v>
       </c>
@@ -30333,7 +30333,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="471" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="471" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="2" t="s">
         <v>38</v>
       </c>
@@ -30359,7 +30359,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="472" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="472" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="2" t="s">
         <v>18</v>
       </c>
@@ -30385,7 +30385,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="473" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="473" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2" t="s">
         <v>63</v>
       </c>
@@ -30411,7 +30411,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="474" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="474" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="2" t="s">
         <v>43</v>
       </c>
@@ -30437,7 +30437,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="475" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="475" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="2" t="s">
         <v>18</v>
       </c>
@@ -30463,7 +30463,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="476" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="476" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="2" t="s">
         <v>43</v>
       </c>
@@ -30489,7 +30489,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="477" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="477" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2" t="s">
         <v>48</v>
       </c>
@@ -30515,7 +30515,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="478" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="478" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="2" t="s">
         <v>63</v>
       </c>
@@ -30541,7 +30541,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="479" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="479" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="2" t="s">
         <v>38</v>
       </c>
@@ -30567,7 +30567,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="480" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="2" t="s">
         <v>43</v>
       </c>
@@ -30593,7 +30593,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="481" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="481" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="2" t="s">
         <v>138</v>
       </c>
@@ -30619,7 +30619,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="482" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="482" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2" t="s">
         <v>43</v>
       </c>
@@ -30645,7 +30645,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="483" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="483" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="2" t="s">
         <v>18</v>
       </c>
@@ -30671,7 +30671,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="484" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="2" t="s">
         <v>38</v>
       </c>
@@ -30697,7 +30697,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="485" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="2" t="s">
         <v>56</v>
       </c>
@@ -30723,7 +30723,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="486" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="486" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="2" t="s">
         <v>63</v>
       </c>
@@ -30749,7 +30749,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="487" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="487" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="2" t="s">
         <v>11</v>
       </c>
@@ -30775,7 +30775,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="488" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="488" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="2" t="s">
         <v>38</v>
       </c>
@@ -30801,7 +30801,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="489" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="489" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="2" t="s">
         <v>38</v>
       </c>
@@ -30827,7 +30827,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="490" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="490" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="2" t="s">
         <v>18</v>
       </c>
@@ -30853,7 +30853,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="491" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="491" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="2" t="s">
         <v>63</v>
       </c>
@@ -30879,7 +30879,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="492" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="492" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="2" t="s">
         <v>43</v>
       </c>
@@ -30905,7 +30905,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="493" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="493" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="2" t="s">
         <v>18</v>
       </c>
@@ -30931,7 +30931,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="494" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="494" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="2" t="s">
         <v>35</v>
       </c>
@@ -30957,7 +30957,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="495" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="495" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="2" t="s">
         <v>43</v>
       </c>
@@ -30983,7 +30983,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="496" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="496" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="2" t="s">
         <v>30</v>
       </c>
@@ -31006,7 +31006,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="497" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="497" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2" t="s">
         <v>43</v>
       </c>
@@ -31038,7 +31038,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="498" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="498" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="2" t="s">
         <v>38</v>
       </c>
@@ -31064,7 +31064,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="499" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="499" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="2" t="s">
         <v>50</v>
       </c>
@@ -31090,7 +31090,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="500" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="500" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="2" t="s">
         <v>50</v>
       </c>
@@ -31116,7 +31116,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="501" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="501" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="2" t="s">
         <v>18</v>
       </c>
@@ -31148,7 +31148,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="502" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="502" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="2" t="s">
         <v>258</v>
       </c>
@@ -31180,7 +31180,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="503" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="503" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="2" t="s">
         <v>43</v>
       </c>
@@ -31212,7 +31212,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="504" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="504" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="2" t="s">
         <v>38</v>
       </c>
@@ -31238,7 +31238,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="505" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="505" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="2" t="s">
         <v>38</v>
       </c>
@@ -31264,7 +31264,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="506" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="506" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="2" t="s">
         <v>32</v>
       </c>
@@ -31290,7 +31290,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="507" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="507" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="2" t="s">
         <v>56</v>
       </c>
@@ -31316,7 +31316,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="508" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="508" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="2" t="s">
         <v>38</v>
       </c>
@@ -31351,7 +31351,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="509" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="509" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="2" t="s">
         <v>52</v>
       </c>
@@ -31377,7 +31377,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="510" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="510" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="2" t="s">
         <v>18</v>
       </c>
@@ -31403,7 +31403,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="511" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="511" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="2" t="s">
         <v>56</v>
       </c>
@@ -31429,7 +31429,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="512" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="512" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="2" t="s">
         <v>43</v>
       </c>
@@ -31455,7 +31455,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="513" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="513" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="2" t="s">
         <v>56</v>
       </c>
@@ -31487,7 +31487,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="514" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="514" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="2" t="s">
         <v>43</v>
       </c>
@@ -31513,7 +31513,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="515" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="515" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="2" t="s">
         <v>134</v>
       </c>
@@ -31539,7 +31539,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="516" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="516" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="2" t="s">
         <v>18</v>
       </c>
@@ -31571,7 +31571,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="517" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="517" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="2" t="s">
         <v>18</v>
       </c>
@@ -31597,7 +31597,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="518" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="518" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="2" t="s">
         <v>18</v>
       </c>
@@ -31623,7 +31623,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="519" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="519" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="2" t="s">
         <v>18</v>
       </c>
@@ -31649,7 +31649,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="520" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="520" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="2" t="s">
         <v>18</v>
       </c>
@@ -31675,7 +31675,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="521" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="521" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="2" t="s">
         <v>28</v>
       </c>
@@ -31710,7 +31710,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="522" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="522" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="2" t="s">
         <v>38</v>
       </c>
@@ -31745,7 +31745,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="523" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="523" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="2" t="s">
         <v>38</v>
       </c>
@@ -31777,7 +31777,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="524" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="524" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="2" t="s">
         <v>38</v>
       </c>
@@ -31803,7 +31803,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="525" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="525" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="2" t="s">
         <v>50</v>
       </c>
@@ -31835,7 +31835,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="526" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="526" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="2" t="s">
         <v>50</v>
       </c>
@@ -31867,7 +31867,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="527" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="527" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2" t="s">
         <v>50</v>
       </c>
@@ -31902,7 +31902,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="528" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="528" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="2" t="s">
         <v>50</v>
       </c>
@@ -31928,7 +31928,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="529" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="529" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="2" t="s">
         <v>51</v>
       </c>
@@ -31960,7 +31960,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="530" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="530" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="2" t="s">
         <v>56</v>
       </c>
@@ -31995,7 +31995,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="531" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="531" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="2" t="s">
         <v>56</v>
       </c>
@@ -32030,7 +32030,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="532" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="532" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="2" t="s">
         <v>56</v>
       </c>
@@ -32056,7 +32056,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="533" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="533" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="2" t="s">
         <v>275</v>
       </c>
@@ -32088,7 +32088,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="534" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="534" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="2" t="s">
         <v>275</v>
       </c>
@@ -32120,7 +32120,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="535" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="535" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="2" t="s">
         <v>43</v>
       </c>
@@ -32152,7 +32152,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="536" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="536" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="2" t="s">
         <v>43</v>
       </c>
@@ -32184,7 +32184,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="537" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="537" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="2" t="s">
         <v>43</v>
       </c>
@@ -32219,7 +32219,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="538" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="538" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="2" t="s">
         <v>43</v>
       </c>
@@ -32245,7 +32245,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="539" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="539" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="2" t="s">
         <v>130</v>
       </c>
@@ -32272,13 +32272,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K539">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="ELB 28"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K539"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
